--- a/rover_platform_mbse/export/ROVER-A1-ROVER_TWIST_MUX-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_TWIST_MUX-SWRS-V-001.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/config/rover_twist_mux.yaml:8; rover_twist_mux/config/rover_twist_mux.yaml:14; rover_twist_mux/config/rover_twist_mux.yaml:18; rover_twist_mux/config/rover_twist_mux.yaml:23; rover_crsf_teleop/launch/rover_crsf_teleop.launch.py:30-33; rover_controller/config/wheel_01_controller.yaml:192</t>
+          <t>rover_twist_mux/config/rover_twist_mux.yaml:8; rover_twist_mux/config/rover_twist_mux.yaml:14; rover_twist_mux/config/rover_twist_mux.yaml:18; rover_twist_mux/config/rover_twist_mux.yaml:23; rover_crsf_teleop/launch/rover_crsf_teleop.launch.py:32-35; rover_controller/config/wheel_01_controller.yaml:192</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_TWIST_MUX-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_TWIST_MUX-SWRS-V-001.xlsx
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
